--- a/Objective 2/analyses/functional_groups/fishtraits_newspecies.xlsx
+++ b/Objective 2/analyses/functional_groups/fishtraits_newspecies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmbet\Documents\GitHub\DGS-Patterns-of-Fish-Diversity\Objective 2\analyses\functional_groups\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{467DD49F-8BC0-4163-9176-7D094B7A667A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DEC97F6-114B-467C-8F59-1E78C50AD205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11355" yWindow="0" windowWidth="10328" windowHeight="13583" xr2:uid="{2F3B665D-9A8A-41F2-B61B-1A80674313B5}"/>
+    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="13583" xr2:uid="{2F3B665D-9A8A-41F2-B61B-1A80674313B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,34 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
-  <si>
-    <t>Etheostoma akatulo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">,Etheostoma chienense, </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Etheostoma cyanoprosopum,</t>
-  </si>
-  <si>
-    <t>Etheostoma sagitta spilotum,</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Lepidomeda copei</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Macrhybopsis tetranema, </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Micropterus velox, </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Nothonotus rubrus, </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Richardsonius egregious,</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
   <si>
     <t>GENUS</t>
   </si>
@@ -152,9 +125,6 @@
     <t>Oregonichthys</t>
   </si>
   <si>
-    <t xml:space="preserve"> kalawatseti</t>
-  </si>
-  <si>
     <t>Umpqua chub</t>
   </si>
   <si>
@@ -164,9 +134,6 @@
     <t>Chrosomus</t>
   </si>
   <si>
-    <t xml:space="preserve"> saylori</t>
-  </si>
-  <si>
     <t>Laurel dace</t>
   </si>
   <si>
@@ -189,6 +156,30 @@
   </si>
   <si>
     <t>Carmine shiner</t>
+  </si>
+  <si>
+    <t>spilotum</t>
+  </si>
+  <si>
+    <t>kentucky arrow darter</t>
+  </si>
+  <si>
+    <t>Kentucky Arrow Darter 5-Year Status Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Etheostoma</t>
+  </si>
+  <si>
+    <t>cyanoprosopum</t>
+  </si>
+  <si>
+    <t>blueface darter</t>
+  </si>
+  <si>
+    <t>saylori</t>
+  </si>
+  <si>
+    <t>kalawatseti</t>
   </si>
 </sst>
 </file>
@@ -198,18 +189,13 @@
   <numFmts count="1">
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Lucida Console"/>
-      <family val="3"/>
     </font>
     <font>
       <sz val="10"/>
@@ -295,42 +281,39 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -667,496 +650,572 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E8EFE48-B364-4EE9-8393-6B5FAB72CFAD}">
-  <dimension ref="A1:T28"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="24.265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.46484375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="10" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="N1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="O1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="P1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="Q1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="R1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="S1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" s="7" t="s">
+      <c r="T1" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G2">
+        <v>-999</v>
+      </c>
+      <c r="H2">
+        <v>-999</v>
+      </c>
+      <c r="I2">
+        <v>-999</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G3">
+        <v>-999</v>
+      </c>
+      <c r="H3">
+        <v>-999</v>
+      </c>
+      <c r="I3">
+        <v>-999</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s">
         <v>25</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="C4" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>5.4</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>189</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="M1" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="N1" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="O1" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="P1" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="R1" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="S1" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="T1" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" ht="15" x14ac:dyDescent="0.45">
-      <c r="A2" s="1"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
         <v>41</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>-999</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="G5">
-        <v>-999</v>
-      </c>
-      <c r="H5">
-        <v>-999</v>
-      </c>
-      <c r="I5">
-        <v>-999</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>1</v>
-      </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
-      <c r="R5">
-        <v>1</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>16.3</v>
+      </c>
+      <c r="G6">
+        <v>0.25</v>
+      </c>
+      <c r="H6" s="10">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>-999</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6" s="11" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>0</v>
+        <v>37</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>-999</v>
+      </c>
+      <c r="H7">
+        <v>-999</v>
+      </c>
+      <c r="I7">
+        <v>-999</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <v>-999</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>-999</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8" s="11" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s">
         <v>33</v>
       </c>
-      <c r="B11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="C9" t="s">
         <v>35</v>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>5.4</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
-        <v>2</v>
-      </c>
-      <c r="I11">
-        <v>189</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>1</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>1</v>
-      </c>
-      <c r="N11">
-        <v>1</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>1</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11" s="12" t="s">
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>15</v>
+      </c>
+      <c r="G9">
+        <v>-999</v>
+      </c>
+      <c r="H9">
+        <v>-999</v>
+      </c>
+      <c r="I9">
+        <v>-999</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9" s="11" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A14" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="F14">
-        <v>16.3</v>
-      </c>
-      <c r="G14">
-        <v>0.25</v>
-      </c>
-      <c r="H14" s="11">
-        <v>2</v>
-      </c>
-      <c r="I14">
-        <v>-999</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>1</v>
-      </c>
-      <c r="M14">
-        <v>1</v>
-      </c>
-      <c r="N14">
-        <v>1</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>1</v>
-      </c>
-      <c r="Q14">
-        <v>1</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14" s="12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>48</v>
-      </c>
-      <c r="B21" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>1</v>
-      </c>
-      <c r="F21">
-        <v>6</v>
-      </c>
-      <c r="G21">
-        <v>-999</v>
-      </c>
-      <c r="H21">
-        <v>-999</v>
-      </c>
-      <c r="I21">
-        <v>-999</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>1</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>1</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
-      <c r="E25">
-        <v>1</v>
-      </c>
-      <c r="F25">
-        <v>15</v>
-      </c>
-      <c r="G25">
-        <v>-999</v>
-      </c>
-      <c r="H25">
-        <v>5</v>
-      </c>
-      <c r="I25">
-        <v>-999</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>1</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>1</v>
-      </c>
-      <c r="N25">
-        <v>1</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25">
-        <v>1</v>
-      </c>
-      <c r="Q25">
-        <v>1</v>
-      </c>
-      <c r="R25">
-        <v>1</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="T25" s="12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>45</v>
-      </c>
-      <c r="B27" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" t="s">
-        <v>46</v>
-      </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
-      <c r="E27">
-        <v>1</v>
-      </c>
-      <c r="F27">
-        <v>15</v>
-      </c>
-      <c r="G27">
-        <v>-999</v>
-      </c>
-      <c r="H27">
-        <v>-999</v>
-      </c>
-      <c r="I27">
-        <v>-999</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>1</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <v>1</v>
-      </c>
-      <c r="N27">
-        <v>1</v>
-      </c>
-      <c r="O27">
-        <v>0</v>
-      </c>
-      <c r="P27">
-        <v>0</v>
-      </c>
-      <c r="Q27">
-        <v>0</v>
-      </c>
-      <c r="R27">
-        <v>1</v>
-      </c>
-      <c r="S27">
-        <v>1</v>
-      </c>
-      <c r="T27" s="12" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="T14" r:id="rId1" display="https://pubs.usgs.gov/publication/70256447" xr:uid="{E9AF1FF6-AC61-473F-A54B-F2C541EF5601}"/>
-    <hyperlink ref="T11" r:id="rId2" display="https://www.conservationfisheries.org/darters/tuxedo-darter" xr:uid="{4B7660DA-58AF-47AF-BAFF-6339AE0CD66B}"/>
-    <hyperlink ref="T25" r:id="rId3" display="https://www.jstor.org/stable/1446578" xr:uid="{B8EF9981-ED74-45FF-B761-18F474084E55}"/>
-    <hyperlink ref="T27" r:id="rId4" display="https://www.mapress.com/zt/article/view/zootaxa.5249.5.1/50089" xr:uid="{333CEC44-7E2A-4E33-A0DF-94FE8C5BB13D}"/>
+    <hyperlink ref="T6" r:id="rId1" display="https://pubs.usgs.gov/publication/70256447" xr:uid="{E9AF1FF6-AC61-473F-A54B-F2C541EF5601}"/>
+    <hyperlink ref="T4" r:id="rId2" display="https://www.conservationfisheries.org/darters/tuxedo-darter" xr:uid="{4B7660DA-58AF-47AF-BAFF-6339AE0CD66B}"/>
+    <hyperlink ref="T8" r:id="rId3" display="https://www.jstor.org/stable/1446578" xr:uid="{B8EF9981-ED74-45FF-B761-18F474084E55}"/>
+    <hyperlink ref="T9" r:id="rId4" display="https://www.mapress.com/zt/article/view/zootaxa.5249.5.1/50089" xr:uid="{333CEC44-7E2A-4E33-A0DF-94FE8C5BB13D}"/>
+    <hyperlink ref="T5" r:id="rId5" display="https://ecosphere-documents-production-public.s3.amazonaws.com/sams/public_docs/species_nonpublish/3978.pdf" xr:uid="{7DABF557-27FF-4ADB-ACC4-D4CC04BEC06F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId5"/>
+  <pageSetup orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>